--- a/data/seed/portfolio/L-2024-6514/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-6514/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I164"/>
+  <dimension ref="A1:I177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -558,33 +558,33 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>1601000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>3347000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>323219853</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3265 за поставленный товар</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №6192</t>
         </is>
       </c>
     </row>
@@ -601,38 +601,38 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>21318000</v>
+        <v>2908000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nurafshon Plastik MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>383427743</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000465334206001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5776 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3696 03.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>05.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -641,39 +641,34 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>15147000</v>
+        <v>7200000</v>
       </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>266730316</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6514)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>16307000314508813417</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3257</t>
+          <t>Kredit shartnomasi L-2024-6514 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -681,28 +676,33 @@
           <t>103</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n">
+        <v>19121000</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6514)</t>
+          <t>Buxoro Metall AJ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>16307000314508813417</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6514 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5204</t>
         </is>
       </c>
     </row>
@@ -719,31 +719,31 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>5689000</v>
+        <v>14147000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9395 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6854 06.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -760,31 +760,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>3566000</v>
+        <v>3965000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №485 06.07.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2245</t>
         </is>
       </c>
     </row>
@@ -801,31 +801,31 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>687000</v>
+        <v>1518000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Bunyodkor Plastik XK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>207746667</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000630329030001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №209 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №149/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -841,34 +841,39 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>13325000</v>
+        <v>5823000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Ishonch Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ish haqi, reestr №3695</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №231/26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -876,23 +881,18 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>11648000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>13325000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jizzax Qurilish Materiallari AJ</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>239198031</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000855339741001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3626</t>
+          <t>Iyun oyi uchun ish haqi, reestr №3926</t>
         </is>
       </c>
     </row>
@@ -919,31 +919,31 @@
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>4651000</v>
+        <v>17280000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>323219853</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8934 от 07.07.2026, в т.ч. НДС 12%</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №9206 07.07.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
@@ -958,40 +958,40 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>3899000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>7555000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olmaliq Meva-Sabzavot MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>204320931</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000857734694001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5365</t>
+          <t>Оплата за продукцию по договору №2/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,39 +1000,39 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>13299000</v>
+        <v>24584000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №286/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №34/26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1042,21 +1042,21 @@
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>1488000</v>
+        <v>13641000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bunyodkor Dori-Darmon MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>202359931</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000852133988001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7348 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1158</t>
         </is>
       </c>
     </row>
@@ -1081,40 +1081,40 @@
           <t>113</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>1472000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>1314000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lazzat Polimer MChJ</t>
+          <t>Sarbon Qurilish MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>362731408</t>
+          <t>214794898</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000762394130001</t>
+          <t>20208000289700209001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1723 за поставленный товар</t>
+          <t>Bino ijarasi uchun to'lov iyul</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1122,33 +1122,33 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>1314000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>2431000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
+          <t>Gulshan Yog'och XK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>278567570</t>
+          <t>242774384</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000480659459001</t>
+          <t>20208000533420645001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8474</t>
         </is>
       </c>
     </row>
@@ -1165,31 +1165,31 @@
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>7368000</v>
+        <v>4164000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazzat Polimer MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>362731408</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000762394130001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №6/26 от 13.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8803</t>
         </is>
       </c>
     </row>
@@ -1206,21 +1206,21 @@
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>2790000</v>
+        <v>2439000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nurafshon Plastik MChJ</t>
+          <t>Bunyodkor Plastik XK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>383427743</t>
+          <t>207746667</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000465334206001</t>
+          <t>20208000630329030001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №58 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan ovar uchun to'lov h/f №9361</t>
         </is>
       </c>
     </row>
@@ -1245,40 +1245,40 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>2140000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>2727000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9273 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №98/26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1288,38 +1288,38 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>1831000</v>
+        <v>13504000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №3854 13.07.2026, QQS BILAN</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2971</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1329,38 +1329,38 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>1485000</v>
+        <v>1750000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №280 13.07.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №18/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1368,40 +1368,40 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>1195000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>1817000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №114/26 от 13.07.2026</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1409,40 +1409,40 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>863000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>1817000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2602 13.07.2026, QQS bilan</t>
+          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1451,39 +1451,39 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>2861000</v>
+        <v>3461000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8797</t>
+          <t>Tovarlar uchun to'lov h/f №9039</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1492,39 +1492,39 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6072000</v>
+        <v>10748000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yangi Hayot Agro MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>252881395</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000726554045001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №83/26 от 13.07.2026, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №264/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1534,38 +1534,38 @@
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>1974000</v>
+        <v>1359000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1961 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №212/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1575,38 +1575,38 @@
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>722000</v>
+        <v>11029000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №303 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2682 20.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1616,38 +1616,38 @@
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>10306000</v>
+        <v>5327000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дговору №217/26 от 16.07.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №710 20.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1657,38 +1657,38 @@
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>2411000</v>
+        <v>4878000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8166</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9225 20.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1698,38 +1698,38 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>718000</v>
+        <v>2587000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Shartnoma №49/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4190</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1737,40 +1737,40 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>1817000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>2405000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №214/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1778,40 +1778,40 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>1817000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>2086000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4387</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1819,40 +1819,40 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>18042000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>6224000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>323219853</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №142/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №260/26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1860,40 +1860,40 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>2515000</v>
-      </c>
+      <c r="C42" s="2" t="n">
+        <v>7709000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Durdona Sut MChJ</t>
+          <t>Afrosiyob Savdo MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>272077466</t>
+          <t>284833327</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000786303290001</t>
+          <t>20208000043472539001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №298/26 от 17.07.2026</t>
+          <t>Предоплата за материалы по договору №279/26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1903,38 +1903,38 @@
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>1871000</v>
+        <v>10133000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Gulshan Yog'och XK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>242774384</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000533420645001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №134/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №8337 от 21.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1944,38 +1944,38 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>1598000</v>
+        <v>1797000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>323219853</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6037 от 17.07.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №187/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,23 +1983,23 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>951000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>4560000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
+          <t>Zafar Plastik MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>323219853</t>
+          <t>363685585</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>20208000860504283001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2009,14 +2009,14 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №68/26 от 17.07.2026</t>
+          <t>Предоплата за материалы по дог. №4/26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2024,40 +2024,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>10227000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>5318000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8413 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №150/26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2065,40 +2065,40 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>1612000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>28894000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №70/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №211/26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2108,38 +2108,38 @@
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>1484000</v>
+        <v>4231000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Shartnoma №107/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №127/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2149,38 +2149,38 @@
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>1439000</v>
+        <v>3235000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Qarshi Sut Mahsulotlari AJ</t>
+          <t>Farg'ona Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>214812567</t>
+          <t>273140807</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000469768447001</t>
+          <t>20208000239413037001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №174/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №262/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2188,40 +2188,40 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>959000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>821000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Durdona Sut MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>272077466</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000786303290001</t>
+          <t>20208000862212128001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №236/26 от 20.07.2026</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2230,39 +2230,39 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>17839000</v>
+        <v>2135000</v>
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №7970</t>
+          <t>QQS iyun 2026 uchun</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2270,23 +2270,23 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>3707000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>14873000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Yulduz Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>290107566</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000251317275001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2296,14 +2296,14 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №70/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №1981</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2311,40 +2311,40 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>2154000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>4300000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>SHARTNOMA №195/26 BO'YICHA OLDINDA TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2352,40 +2352,40 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>821000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>9963000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000512925234001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за июль 2026 г.</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №225 27.07.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>3040000</v>
+        <v>1720000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №8727 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9645 27.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2435,32 +2435,32 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>3054000</v>
+        <v>3521000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Afrosiyob Savdo MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>284833327</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000043472539001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5340</t>
+          <t>Оплата за сырье по дог. №265/26 от 27.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2475,33 +2475,33 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>6732000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>4350000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Qarshi Sut Mahsulotlari AJ</t>
+          <t>Kattaqo'rg'on Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>214812567</t>
+          <t>397496536</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000469768447001</t>
+          <t>20208000722221498001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №208/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №8961</t>
         </is>
       </c>
     </row>
@@ -2516,40 +2516,40 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>5530000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>20711000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>323219853</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №143/26, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №124/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2559,38 +2559,38 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>5145000</v>
+        <v>2497000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Bunyodkor Plastik XK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>207746667</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000630329030001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7778 27.07.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4893</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2600,38 +2600,38 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>3936000</v>
+        <v>1922000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2254 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4458 28.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2641,38 +2641,38 @@
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>2353000</v>
+        <v>1900000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lazzat Polimer MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>362731408</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000762394130001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6012 за поставленный товар</t>
+          <t>Предоплата за товар по договору №107/26 от 28.07.2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2682,38 +2682,38 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>754000</v>
+        <v>2159000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6467 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6373</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2721,40 +2721,35 @@
           <t>153</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>2569000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>380262596</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3795 за поставленный товар</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2762,23 +2757,23 @@
           <t>154</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>2285000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>27399000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2788,14 +2783,14 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №2932</t>
+          <t>Shartnoma №82/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2804,39 +2799,39 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>6056000</v>
+        <v>4369000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Nihol Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>280408161</t>
+          <t>269439592</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000055865845001</t>
+          <t>20208000927817832001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №243/26 от 29.07.2026, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №231/26</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2846,38 +2841,38 @@
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>11621000</v>
+        <v>2644000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4499 за поставленный товар</t>
+          <t>Shartnoma №83/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2885,40 +2880,35 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>2526000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>380262596</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6514)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>16307000314508813417</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №952 от 30.07.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-6514 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2927,39 +2917,39 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>10021000</v>
+        <v>16876000</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Yangi Hayot Agro MChJ</t>
+          <t>Barakali Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>252881395</t>
+          <t>367570348</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000726554045001</t>
+          <t>20208000659459751001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №38/26 от 30.07.2026, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №299/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2967,40 +2957,35 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>3987000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>14011000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>380262596</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №221/26, QQS 12%</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3010,38 +2995,38 @@
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>1003000</v>
+        <v>9111000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nurafshon Plastik MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>383427743</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000465334206001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2248 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №6883 ОТ 07.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3049,35 +3034,40 @@
           <t>161</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>3846000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Buxoro Metall AJ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1971 07.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3086,39 +3076,39 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>9229000</v>
+        <v>1381000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Sarbon Qurilish MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>214794898</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000289700209001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №92/26</t>
+          <t>Аренда помещения за август, дог. №38/22</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3127,39 +3117,39 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>57526000</v>
+        <v>3408000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7713</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №194/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3169,38 +3159,38 @@
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>8792000</v>
+        <v>12737000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>323219853</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5208 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2535 10.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3210,38 +3200,38 @@
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>4903000</v>
+        <v>7015000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Shartnoma №24/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №195/26 от 10.08.2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3251,38 +3241,38 @@
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>4697000</v>
+        <v>2977000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №143/26 от 03.08.2026</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №153/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3292,38 +3282,38 @@
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>4305000</v>
+        <v>3237000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4406 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №243/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3333,38 +3323,38 @@
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>2757000</v>
+        <v>3141000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>323219853</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6758</t>
+          <t>Tovar uchun to'lov, h/f №6657 11.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3372,40 +3362,40 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>2386000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>19864000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4137 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №80/26</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3413,40 +3403,40 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>6987000</v>
-      </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n">
+        <v>11216000</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Yangi Hayot Agro MChJ</t>
+          <t>Gulshan Yog'och XK</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>252881395</t>
+          <t>242774384</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000726554045001</t>
+          <t>20208000533420645001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №148/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №58/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3456,38 +3446,38 @@
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>3377000</v>
+        <v>13129000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №3403 от 04.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №2595 14.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3496,39 +3486,39 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>31871000</v>
+        <v>1911000</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Marg'ilon Agro Servis XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>302224574</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000799592285001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №102/26</t>
+          <t>Ijtimoiy soliq iyul 2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3536,40 +3526,40 @@
           <t>173</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>6101000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>1911000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №296/26 от 05.08.2026</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3579,38 +3569,38 @@
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>2167000</v>
+        <v>4117000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №218/26 от 05.08.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4593</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3618,35 +3608,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>3564000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6514)</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>16307000314508813417</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6514 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9864 17.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3655,34 +3650,39 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>14011000</v>
+        <v>49950000</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Ishonch Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №7406</t>
+          <t>Оплата за товары согласно с/ф №9671</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3692,38 +3692,38 @@
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>2103000</v>
+        <v>7295000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
+          <t>Qo'qon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>323219853</t>
+          <t>319803148</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>20208000533974181001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №276/26 от 07.08.2026</t>
+          <t>SHARTNOMA №237/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3731,40 +3731,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>1381000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>4406000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>278567570</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000480659459001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по договору №49/23</t>
+          <t>Shartnoma №35/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3774,38 +3774,38 @@
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>12908000</v>
+        <v>4318000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
+          <t>Bunyodkor Plastik XK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>323219853</t>
+          <t>207746667</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>20208000630329030001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9616 за поставленный товар</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №2741 20.08.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3815,38 +3815,38 @@
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>1770000</v>
+        <v>4158000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Qo'qon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>319803148</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000533974181001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4807 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №228/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3855,22 +3855,22 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>7896000</v>
+        <v>4918000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Barakali Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>367570348</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000659459751001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3880,14 +3880,14 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №9892</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №93/26</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3895,23 +3895,23 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>15193000</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n">
+        <v>6820000</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №68/26</t>
+          <t>Оплата за товар по счет-фактуре №310 от 21.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3937,39 +3937,39 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>51171000</v>
+        <v>3805000</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Yangi Hayot Agro MChJ</t>
+          <t>Afrosiyob Savdo MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>252881395</t>
+          <t>284833327</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000726554045001</t>
+          <t>20208000043472539001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договоу №296/26 от 10.08.2026, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №95/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3977,40 +3977,40 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>11250000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>19276000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Yangi Hayot Agro MChJ</t>
+          <t>Gulshan Yog'och XK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>252881395</t>
+          <t>242774384</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000726554045001</t>
+          <t>20208000533420645001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, сф №5324</t>
+          <t>Shartnoma №17/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4020,38 +4020,38 @@
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>9127000</v>
+        <v>3619000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nurafshon Plastik MChJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>383427743</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000465334206001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №177/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №155/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4061,21 +4061,21 @@
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>1957000</v>
+        <v>2922000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Durdona Sut MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>272077466</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000786303290001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4085,14 +4085,14 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №22/26 ОТ 17.08.2026</t>
+          <t>Оплата за товар по с/ф №7102 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1911000</v>
+        <v>2297000</v>
       </c>
       <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
@@ -4126,14 +4126,14 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4142,39 +4142,39 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1911000</v>
+        <v>3755000</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Afrosiyob Savdo MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>284833327</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000043472539001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>НДФЛ ЗА ИЮЛЬ 2026</t>
+          <t>Tovarlar uchun to'lov h/f №1974</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4183,39 +4183,39 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>6434000</v>
+        <v>7884000</v>
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Kattaqo'rg'on Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>397496536</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000722221498001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3208</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №279/26</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4224,39 +4224,39 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>6754000</v>
+        <v>863000</v>
       </c>
       <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000862212128001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №144/26 от 17.08.2026, НДС 12%</t>
+          <t>Elektr energiyasiuchun to'lov avgust</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4266,21 +4266,21 @@
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>8529000</v>
+        <v>7322000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Durdona Sut MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>272077466</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000786303290001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4290,14 +4290,14 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №171/26 от 18.08.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8516 28.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4307,21 +4307,21 @@
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>2950000</v>
+        <v>3913000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Durdona Sut MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>272077466</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000786303290001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4331,14 +4331,14 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1963 за поставленный товар</t>
+          <t>Shartnoma №82/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4346,40 +4346,40 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>2575000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>12668000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №7/26 от 18.08.2026</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №161/26</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4389,38 +4389,38 @@
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>3849000</v>
+        <v>16344000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2383</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5147</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4430,38 +4430,38 @@
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>4567000</v>
+        <v>3873000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7275 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №93</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4471,38 +4471,38 @@
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>3563000</v>
+        <v>3038000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>323219853</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4873 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9564</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4510,40 +4510,35 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>2892000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>323219853</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №273/26 от 24.08.2026</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4552,39 +4547,39 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>863000</v>
+        <v>2549000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Zafar Plastik MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>363685585</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000512925234001</t>
+          <t>20208000860504283001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov avgust</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №54/26</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4593,39 +4588,39 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>2241000</v>
+        <v>13184000</v>
       </c>
       <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>QO'SHILGAN QIYMAT SOLIG'I IYUL OYI</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №160/26</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4633,40 +4628,40 @@
           <t>200</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>10945000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>17241000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lazzat Polimer MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>362731408</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000762394130001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №90/26 от 25.08.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №202/26</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4674,40 +4669,40 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>23391000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>1779000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Samarqand Yog' Zavodi MChJ</t>
+          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>220848333</t>
+          <t>222457427</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000740434725001</t>
+          <t>20208000959228598001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7033</t>
+          <t>Оплата по с/ф №5071 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4715,23 +4710,23 @@
           <t>202</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>5898000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>11150000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lazzat Poligraf MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>249360834</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000385031386001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4741,14 +4736,14 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №113/26 от 26.08.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №15/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4758,38 +4753,38 @@
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>1938000</v>
+        <v>8705000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Gulshan Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>340132877</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000945666007001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №8719 за поставленный товар</t>
+          <t>Shartnoma №136/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4797,23 +4792,23 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>24905000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>6298000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Yulduz Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>290107566</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000251317275001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4823,14 +4818,14 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №75/26, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №28/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4838,40 +4833,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>20978000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>6999000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Lazzat Poligraf MChJ</t>
+          <t>Afrosiyob Savdo MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>249360834</t>
+          <t>284833327</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000385031386001</t>
+          <t>20208000043472539001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №112/26 от 31.08.2026</t>
+          <t>Tovarlar uchun to'lov h/f №7160</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>05.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4879,40 +4874,35 @@
           <t>206</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n">
-        <v>18338000</v>
-      </c>
+      <c r="C116" s="2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>380262596</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6514)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>16307000314508813417</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №199/26, НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-6514 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4922,38 +4912,38 @@
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>7511000</v>
+        <v>4913000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Bunyodkor Plastik XK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>207746667</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000630329030001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №231/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №183/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4962,34 +4952,39 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>300000</v>
+        <v>4630000</v>
       </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Zafar Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>363685585</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000860504283001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Xom ashyo uchun to'lov, shartn. №193/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4997,40 +4992,35 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>6731000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>14842000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>380262596</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №166/26 от 02.09.2026</t>
+          <t>Avgust oyi uchun ish haqi, reestr №9105</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5038,40 +5028,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>5866000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>29895000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №2257 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №176/26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5081,38 +5071,38 @@
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>20504000</v>
+        <v>5820000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Bunyodkor Plastik XK</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>207746667</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000630329030001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2859 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №9/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5120,40 +5110,40 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>5106000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Angren Tur Servis MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>349210815</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000780204492001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7111</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7398</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5161,40 +5151,40 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>2010000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>2594000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Yangi Hayot Agro MChJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>252881395</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000726554045001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3197</t>
+          <t>Оплата по счет-фактуре №9709 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5203,34 +5193,39 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>7200000</v>
+        <v>1463000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6514)</t>
+          <t>Sarbon Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>214794898</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>16307000314508813417</t>
+          <t>20208000289700209001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6514 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Ijara haqi sentyabr oyi uchun, shartnoma №38/22</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5238,40 +5233,40 @@
           <t>215</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v>990000</v>
-      </c>
-      <c r="D125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n">
+        <v>11288000</v>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Samarqand Yog' Zavodi MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>220848333</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000740434725001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №46/26</t>
+          <t>Оплата за товар по счет-фактуре №7636 от 10.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5279,23 +5274,23 @@
           <t>216</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>1328000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>1825000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Olmaliq Meva-Sabzavot MChJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>204320931</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000857734694001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5305,14 +5300,14 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2452</t>
+          <t>Оплата за товар по счет-фактуре №49 от 10.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5320,23 +5315,23 @@
           <t>217</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>2438000</v>
-      </c>
-      <c r="D127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n">
+        <v>1329000</v>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>280408161</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000055865845001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5346,14 +5341,14 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №21/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №7/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5362,34 +5357,39 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>14842000</v>
+        <v>9722000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Zafar Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>363685585</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000860504283001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за август 2026 г. согласно реестру №2401</t>
+          <t>Xom ashyo uchun to'lov, shartn. №82/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5399,38 +5399,38 @@
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>38682000</v>
+        <v>3290000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
+          <t>Gulshan Yog'och XK</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>323219853</t>
+          <t>242774384</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>20208000533420645001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №94/26 от 08.09.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7589 11.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5438,40 +5438,40 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>849000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>1403000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Yangi Hayot Agro MChJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>252881395</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000726554045001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4810</t>
+          <t>Оплата за товар по счет-фактуре №6761 от 11.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5479,40 +5479,40 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>1463000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>1396000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>278567570</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000480659459001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №49/23</t>
+          <t>Mahsulot uchun to'lov, shartnoma №242/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5522,31 +5522,31 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>20685000</v>
+        <v>5030000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Bunyodkor Plastik XK</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>207746667</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000630329030001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №124/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №54/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -5561,40 +5561,40 @@
           <t>223</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>17036000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>5891000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Kamalak Meva Eksport AJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>240816150</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000586584517001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3898 за посталенный товар</t>
+          <t>Tovarlar uchun to'lov h/f №1075</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5604,38 +5604,38 @@
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>6714000</v>
+        <v>9100000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Qarshi Sut Mahsulotlari AJ</t>
+          <t>Gulshan Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>214812567</t>
+          <t>340132877</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000469768447001</t>
+          <t>20208000945666007001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №261/26 от 14.09.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3613</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5643,23 +5643,23 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>463000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>5671000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>280408161</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000055865845001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5669,14 +5669,14 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №198/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №192/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5684,23 +5684,23 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>837000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>2684000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5710,14 +5710,14 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5445</t>
+          <t>Mahsulot uchun to'lov, shartnoma №61/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5725,40 +5725,40 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>1242000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>1735000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Yangi Hayot Agro MChJ</t>
+          <t>Qo'qon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>252881395</t>
+          <t>319803148</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000726554045001</t>
+          <t>20208000533974181001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №41/26 от 14.09.2026, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №9641 от 15.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5792,14 +5792,14 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Ijtimoiy soliq avgust 2026</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5833,14 +5833,14 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>НДФЛ за август 2026</t>
+          <t>JShDS avgust oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5850,21 +5850,21 @@
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>5864000</v>
+        <v>2468000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Durdona Sut MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>272077466</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000786303290001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5874,14 +5874,14 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2295 16.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №122/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5889,40 +5889,40 @@
           <t>231</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>6124000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>1851000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4210</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1684 17.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5932,38 +5932,38 @@
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>11845000</v>
+        <v>7540000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Qo'qon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>319803148</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000533974181001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №62/26, НДС 12%</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №2606 18.09.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5973,38 +5973,38 @@
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>8977000</v>
+        <v>2135000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Jizzax Qurilish Materiallari AJ</t>
+          <t>Bunyodkor Plastik XK</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>239198031</t>
+          <t>207746667</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000855339741001</t>
+          <t>20208000630329030001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №190/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №150/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6014,31 +6014,31 @@
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>6503000</v>
+        <v>1560000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Farg'ona Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>273140807</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000239413037001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №147/26 от 21.09.2026</t>
+          <t>Tovar uchun to'lov, h/f №595 18.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -6053,33 +6053,33 @@
           <t>235</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>772000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>6999000</v>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Samarqand Yog' Zavodi MChJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>220848333</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000740434725001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №129/26</t>
+          <t>Shartnoma №249/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -6095,32 +6095,32 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>796000</v>
+        <v>2365000</v>
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bekobod Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>340901075</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000692513172001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8293</t>
+          <t>QQS avgust 2026 uchun</t>
         </is>
       </c>
     </row>
@@ -6136,32 +6136,32 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>2704000</v>
+        <v>8029000</v>
       </c>
       <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Afrosiyob Savdo MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>284833327</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000043472539001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №246/26</t>
+          <t>Оплата за товары согласно счет-фактуре №9516</t>
         </is>
       </c>
     </row>
@@ -6177,39 +6177,39 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>3009000</v>
+        <v>10152000</v>
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>266730316</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000734126624001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №60/26 от 21.09.2026, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №75/26</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6217,33 +6217,33 @@
           <t>239</t>
         </is>
       </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>9660000</v>
-      </c>
+      <c r="C149" s="2" t="n">
+        <v>18676000</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Durdona Sut MChJ</t>
+          <t>Zafar Plastik MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>272077466</t>
+          <t>363685585</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000786303290001</t>
+          <t>20208000860504283001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №88/26 от 22.09.2026</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №127/26</t>
         </is>
       </c>
     </row>
@@ -6258,40 +6258,40 @@
           <t>240</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n">
-        <v>2419000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>2674000</v>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
+          <t>Оплата за продукцию по договору №37/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6299,33 +6299,33 @@
           <t>241</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>13392000</v>
-      </c>
+      <c r="C151" s="2" t="n">
+        <v>9821000</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4273 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №297/26</t>
         </is>
       </c>
     </row>
@@ -6340,33 +6340,33 @@
           <t>242</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n">
-        <v>690000</v>
-      </c>
-      <c r="D152" s="2" t="n"/>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n">
+        <v>1356000</v>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Angren Tur Servis MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>349210815</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000780204492001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4080</t>
+          <t>Оплата за товар по счет-факуре №4981 от 23.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -6381,40 +6381,40 @@
           <t>243</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n">
-        <v>914000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>1353000</v>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000512925234001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Tovar uchun to'lov, h/f №28 23.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6422,23 +6422,23 @@
           <t>244</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>13830000</v>
-      </c>
+      <c r="C154" s="2" t="n">
+        <v>7742000</v>
+      </c>
+      <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Qarshi Sut Mahsulotlari AJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>214812567</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000469768447001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5842 от 24.09.2026, в т.ч. НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №179/26</t>
         </is>
       </c>
     </row>
@@ -6465,31 +6465,31 @@
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="n">
-        <v>3334000</v>
+        <v>5635000</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Shodlik Sut Mahsulotlari MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>323219853</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000008636493001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №39/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №258/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -6504,40 +6504,40 @@
           <t>246</t>
         </is>
       </c>
-      <c r="C156" s="2" t="n">
-        <v>671000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>2289000</v>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Yangi Hayot Agro MChJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>252881395</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000726554045001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №110/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8622 24.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6546,39 +6546,39 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>778000</v>
+        <v>4340000</v>
       </c>
       <c r="D157" s="2" t="n"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Olmaliq Meva-Sabzavot MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>204320931</t>
+          <t>289423404</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000857734694001</t>
+          <t>20208000196357285001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №183/26, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №167/26</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6586,33 +6586,33 @@
           <t>248</t>
         </is>
       </c>
-      <c r="C158" s="2" t="n">
-        <v>14313000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>7169000</v>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Yangi Hayot Agro MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>252881395</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000726554045001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5153</t>
+          <t>Shartnoma №276/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -6627,40 +6627,40 @@
           <t>249</t>
         </is>
       </c>
-      <c r="C159" s="2" t="n">
-        <v>126603000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>34605000</v>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Nihol Trans Servis AJ</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>265974965</t>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000637222214001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №267/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №224/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6670,21 +6670,21 @@
       </c>
       <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="n">
-        <v>3222000</v>
+        <v>12384000</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Durdona Sut MChJ</t>
+          <t>Buxoro Metall AJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>272077466</t>
+          <t>226259683</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000786303290001</t>
+          <t>20208000296074724001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6694,14 +6694,14 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7290 29.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartn. №155/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6711,38 +6711,38 @@
       </c>
       <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="n">
-        <v>8747000</v>
+        <v>6989000</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Farm Savdo MChJ</t>
+          <t>Gulshan Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>380262596</t>
+          <t>340132877</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000362960747001</t>
+          <t>20208000945666007001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3182 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №413</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6750,54 +6750,587 @@
           <t>252</t>
         </is>
       </c>
-      <c r="C162" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D162" s="2" t="n"/>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>6053000</v>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>221985390</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000863649322001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4995</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C163" s="4" t="n">
-        <v>566104000</v>
-      </c>
-      <c r="D163" s="4" t="n">
-        <v>567904000</v>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>5742000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Buxoro Metall AJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>226259683</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000296074724001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №274/26, QQS 12%</t>
+        </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>3681000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Farg'ona Meva-Sabzavot XK</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>273140807</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000239413037001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4480</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n">
+        <v>3360000</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Gulshan Yog'och XK</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>242774384</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000533420645001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №9989 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n">
+        <v>2832000</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Qo'qon Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>319803148</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000533974181001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №4145 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>1509000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Zarafshon Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>221985390</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000863649322001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartn. №23/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>914000</v>
+      </c>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000862212128001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Elektr energiyasi uchun to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>4185000</v>
+      </c>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Afrosiyob Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>284833327</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000043472539001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №8458</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>5264000</v>
+      </c>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Ishonch Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>289423404</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000196357285001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №275/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>10390000</v>
+      </c>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Zafar Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>363685585</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000860504283001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №171/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n">
+        <v>7072000</v>
+      </c>
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Ishonch Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>289423404</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000196357285001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №52/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n">
+        <v>3234000</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Buxoro Metall AJ</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>226259683</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000296074724001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №429 30.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Zarafshon Kredit Bank</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Bank xizmati uchun komissiya</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v>7362000</v>
+      </c>
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Barakali Meva-Sabzavot XK</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>367570348</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000659459751001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №3855</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="n">
+        <v>564674000</v>
+      </c>
+      <c r="D176" s="4" t="n">
+        <v>566474000</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C164" s="4" t="n">
+      <c r="C177" s="4" t="n">
         <v>15500000</v>
       </c>
-      <c r="D164" s="4" t="n"/>
+      <c r="D177" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
